--- a/indicadores/SFE-GCN_out.xlsx
+++ b/indicadores/SFE-GCN_out.xlsx
@@ -110,7 +110,7 @@
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">ysonder</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
